--- a/upgrade-doc/upgrade/tianji-party/Rundown_CR251203015_DC7_20260413.xlsx
+++ b/upgrade-doc/upgrade/tianji-party/Rundown_CR251203015_DC7_20260413.xlsx
@@ -52,29 +52,31 @@
   </si>
   <si>
     <t>Run upgrade script
-/home/logreader/upgrade/20260409/squid-timeout/upgrade.sh</t>
+/home/logreader/upgrade/20260413/tianji-party/upgrade.sh
+/home/logreader/upgrade/20260413/tianji-party/upgrade-squid.sh</t>
   </si>
   <si>
-    <t>Successfully run upgrade script on poxappprd52a</t>
+    <t>Successfully run upgrade script on poxappprd41a</t>
   </si>
   <si>
     <t>verify upgrade result</t>
   </si>
   <si>
-    <t>Successfully upgrade on poxappprd52a</t>
+    <t>Successfully upgrade on poxappprd41a</t>
   </si>
   <si>
     <t>Run rollback script
-/home/logreader/upgrade/20260409/squid-timeout/rollback.sh</t>
+/home/logreader/upgrade/20260413/tianji-party/rollback.sh
+/home/logreader/upgrade/20260413/tianji-party/rollback-squid.sh</t>
   </si>
   <si>
-    <t>Successfully run fallback script on poxappprd52a</t>
+    <t>Successfully run fallback script on poxappprd41a</t>
   </si>
   <si>
     <t>Verify rollback result</t>
   </si>
   <si>
-    <t>Successfully rollback on poxappprd52a</t>
+    <t>Successfully rollback on poxappprd41a</t>
   </si>
 </sst>
 </file>
@@ -798,7 +800,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10132695" cy="2674620"/>
+          <a:ext cx="10132695" cy="2750820"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -839,7 +841,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10132695" cy="2674620"/>
+          <a:ext cx="10132695" cy="2750820"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -880,7 +882,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10132695" cy="2674620"/>
+          <a:ext cx="10132695" cy="2750820"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -904,21 +906,21 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>561975</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>920115</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2052" name="Object 4" hidden="1">
+            <xdr:cNvPr id="2053" name="Object 5" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2052"/>
+                  <a14:compatExt spid="_x0000_s2053"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -926,7 +928,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="561975" y="1466850"/>
+              <a:off x="561975" y="1362075"/>
               <a:ext cx="923925" cy="838200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -961,10 +963,10 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3075" name="Object 3" hidden="1">
+            <xdr:cNvPr id="3076" name="Object 4" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3075"/>
+                  <a14:compatExt spid="_x0000_s3076"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1229,15 +1231,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="2" customFormat="1" ht="51" customHeight="1" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46121.9583333333</v>
+        <v>46125.9583333333</v>
       </c>
       <c r="C2" s="2">
-        <v>46121.9652777778</v>
+        <v>46125.9791666667</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>6</v>
@@ -1251,10 +1253,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="C3" s="2">
-        <v>46122.0138888889</v>
+        <v>46126.0208333333</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
@@ -1306,19 +1308,19 @@
   <oleObjects>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <oleObject shapeId="2052" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON">
+        <oleObject shapeId="2053" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON">
           <objectPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>561975</xdr:colOff>
-                <xdr:row>4</xdr:row>
+                <xdr:row>3</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>920115</xdr:colOff>
-                <xdr:row>8</xdr:row>
+                <xdr:row>7</xdr:row>
                 <xdr:rowOff>114300</xdr:rowOff>
               </to>
             </anchor>
@@ -1326,7 +1328,7 @@
         </oleObject>
       </mc:Choice>
       <mc:Fallback>
-        <oleObject shapeId="2052" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON"/>
+        <oleObject shapeId="2053" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </oleObjects>
@@ -1371,10 +1373,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46122.0138888889</v>
+        <v>46122.0208333333</v>
       </c>
       <c r="C2" s="2">
-        <v>46122.0208333333</v>
+        <v>46122.0277777778</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>10</v>
@@ -1388,10 +1390,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46122.0208333333</v>
+        <v>46126.0277777778</v>
       </c>
       <c r="C3" s="2">
-        <v>46122.0347222222</v>
+        <v>46126.0416666667</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>12</v>
@@ -1419,7 +1421,7 @@
   <oleObjects>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <oleObject shapeId="3075" progId="Word.Document.8" r:id="rId3" dvAspect="DVASPECT_ICON">
+        <oleObject shapeId="3076" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON">
           <objectPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -1439,7 +1441,7 @@
         </oleObject>
       </mc:Choice>
       <mc:Fallback>
-        <oleObject shapeId="3075" progId="Word.Document.8" r:id="rId3" dvAspect="DVASPECT_ICON"/>
+        <oleObject shapeId="3076" progId="Word.Document.12" r:id="rId3" dvAspect="DVASPECT_ICON"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </oleObjects>
